--- a/conformance/cases/xlsx-05-formulas.xlsx
+++ b/conformance/cases/xlsx-05-formulas.xlsx
@@ -50,7 +50,7 @@
       </c>
       <c r="D2" t="str">
         <f>A1</f>
-        <v>Lane từ công thức</v>
+        <v>Lane from formula</v>
       </c>
     </row>
     <row r="3">
@@ -71,7 +71,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vào</t>
+          <t xml:space="preserve">Enter</t>
         </is>
       </c>
     </row>
@@ -113,7 +113,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xong</t>
+          <t xml:space="preserve">Done</t>
         </is>
       </c>
     </row>
